--- a/artfynd/A 39819-2021 artfynd.xlsx
+++ b/artfynd/A 39819-2021 artfynd.xlsx
@@ -1345,7 +1345,7 @@
         <v>115282931</v>
       </c>
       <c r="B8" t="n">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>115283020</v>
       </c>
       <c r="B12" t="n">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39819-2021 artfynd.xlsx
+++ b/artfynd/A 39819-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115282926</v>
       </c>
       <c r="B2" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,48 +781,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115282932</v>
+        <v>115282935</v>
       </c>
       <c r="B3" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389490</v>
+        <v>389449</v>
       </c>
       <c r="R3" t="n">
-        <v>6589848</v>
+        <v>6589906</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -898,48 +886,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115283011</v>
+        <v>115282995</v>
       </c>
       <c r="B4" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389384</v>
+        <v>389438</v>
       </c>
       <c r="R4" t="n">
-        <v>6589786</v>
+        <v>6589699</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115282997</v>
+        <v>115282949</v>
       </c>
       <c r="B5" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,27 +1002,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1057,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389439</v>
+        <v>389364</v>
       </c>
       <c r="R5" t="n">
-        <v>6589810</v>
+        <v>6589966</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,48 +1101,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115283006</v>
+        <v>115283002</v>
       </c>
       <c r="B6" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1169,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389418</v>
+        <v>389424</v>
       </c>
       <c r="R6" t="n">
-        <v>6589797</v>
+        <v>6589795</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,43 +1206,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115282995</v>
+        <v>115282997</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1279,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389438</v>
+        <v>389439</v>
       </c>
       <c r="R7" t="n">
-        <v>6589699</v>
+        <v>6589810</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115282931</v>
+        <v>115282929</v>
       </c>
       <c r="B8" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389490</v>
+        <v>389494</v>
       </c>
       <c r="R8" t="n">
-        <v>6589848</v>
+        <v>6589860</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1454,15 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115282929</v>
+        <v>115282878</v>
       </c>
       <c r="B9" t="n">
-        <v>4763</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>389494</v>
+        <v>389529</v>
       </c>
       <c r="R9" t="n">
-        <v>6589860</v>
+        <v>6589891</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1566,15 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115282935</v>
+        <v>115282931</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,30 +1536,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389449</v>
+        <v>389490</v>
       </c>
       <c r="R10" t="n">
-        <v>6589906</v>
+        <v>6589848</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,46 +1632,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115283002</v>
+        <v>115283020</v>
       </c>
       <c r="B11" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>389424</v>
+        <v>389363</v>
       </c>
       <c r="R11" t="n">
-        <v>6589795</v>
+        <v>6589773</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,15 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115283020</v>
+        <v>115282932</v>
       </c>
       <c r="B12" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1750,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>389363</v>
+        <v>389490</v>
       </c>
       <c r="R12" t="n">
-        <v>6589773</v>
+        <v>6589848</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,46 +1846,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115282949</v>
+        <v>115283006</v>
       </c>
       <c r="B13" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1945,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>389364</v>
+        <v>389418</v>
       </c>
       <c r="R13" t="n">
-        <v>6589966</v>
+        <v>6589797</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1983,11 +1928,6 @@
           <t>2024-03-19</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2010,6 +1950,235 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115283011</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skönnebolsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>389384</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6589786</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129675893</v>
+      </c>
+      <c r="B15" t="n">
+        <v>109003</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>231856</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trollfibbla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hieracium oistophyllum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pugsley</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skönnebol, SV gården, Skönnebol, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>389684</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6589419</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Vägkant vid lövskogsdunge</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>PAP 550</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39819-2021 artfynd.xlsx
+++ b/artfynd/A 39819-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282949</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282929</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282931</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283020</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115282932</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283006</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283011</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,8 +2249,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129675893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>